--- a/data/trans_orig/P21D6_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127569</t>
+          <t>129242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144266</t>
+          <t>144912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96385</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110262</t>
+          <t>110658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229301</t>
+          <t>229436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250714</t>
+          <t>251412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26697</t>
+          <t>25024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14648</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27987</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28469</t>
+          <t>27709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>49763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>493</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2670</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3164</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2630</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3072</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3493</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>138106</t>
+          <t>141044</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172703</t>
+          <t>172651</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>163469</t>
+          <t>163158</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>187169</t>
+          <t>187475</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>313152</t>
+          <t>311070</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>352009</t>
+          <t>353259</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45708</t>
+          <t>44738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>21031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>40219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44669</t>
+          <t>43916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76878</t>
+          <t>79243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35331</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>21195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38860</t>
+          <t>39575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35975</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63857</t>
+          <t>66391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>14529</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81101</t>
+          <t>80619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91225</t>
+          <t>90794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118029</t>
+          <t>117633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131314</t>
+          <t>131189</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203116</t>
+          <t>203004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219302</t>
+          <t>219975</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>24881</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1596</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1247</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>101396</t>
+          <t>99847</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124693</t>
+          <t>123937</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>201012</t>
+          <t>202792</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>233547</t>
+          <t>234279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>311769</t>
+          <t>312081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>356193</t>
+          <t>356349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>40813</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26754</t>
+          <t>27623</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67301</t>
+          <t>66994</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60422</t>
+          <t>60710</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68596</t>
+          <t>68621</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60448</t>
+          <t>61177</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69685</t>
+          <t>69762</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126128</t>
+          <t>125570</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136816</t>
+          <t>136929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>400</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -3345,97 +3345,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>106803</t>
+          <t>107556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>118870</t>
+          <t>118959</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85317</t>
+          <t>84846</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>97646</t>
+          <t>98231</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>197115</t>
+          <t>196801</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>213883</t>
+          <t>213818</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24727</t>
+          <t>25185</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21388</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37832</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,77 +3821,77 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>2869</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3914,97 +3914,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2745</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>515</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>2136</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>3401</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>262170</t>
+          <t>262544</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>288103</t>
+          <t>288811</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>257722</t>
+          <t>257450</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>279091</t>
+          <t>278571</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>529839</t>
+          <t>528522</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>563329</t>
+          <t>561247</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>45812</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>36996</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>42104</t>
+          <t>43934</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>72604</t>
+          <t>75090</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>103123</t>
+          <t>101127</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>529841</t>
+          <t>528810</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>327641</t>
+          <t>327044</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>339048</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>299848</t>
+          <t>275200</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>865431</t>
+          <t>865303</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>449526</t>
+          <t>452006</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>33554</t>
+          <t>33949</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>602191</t>
+          <t>628377</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>69,6%</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,62 +4974,62 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>11655</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>9656</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5052,82 +5052,82 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>2762</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>788091</t>
+          <t>748311</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1471616</t>
+          <t>1473332</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1357003</t>
+          <t>1362623</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1416388</t>
+          <t>1420515</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1952680</t>
+          <t>2021445</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2857998</t>
+          <t>2867653</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>147523</t>
+          <t>146098</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>851847</t>
+          <t>899489</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,82 +5410,82 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>148365</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>168345</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>524495</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>289109</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>1167496</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
           <t>8,88%</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>51,26%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>148365</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>125826</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>172880</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>10,85%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>524495</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>294341</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>1229180</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>46352</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>50915</t>
+          <t>50773</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>49543</t>
+          <t>50221</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>87328</t>
+          <t>88497</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>39603</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D6_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Provincia-trans_orig.xlsx
@@ -725,12 +725,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>137507</t>
+          <t>138806</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>130863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -740,17 +740,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>104116</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97063</t>
+          <t>106369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110658</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>241623</t>
+          <t>252961</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229436</t>
+          <t>241590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251412</t>
+          <t>262452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16759</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25024</t>
+          <t>23424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20702</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14588</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>31027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49763</t>
+          <t>49809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>487</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>487</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>985</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>985</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>157798</t>
+          <t>165352</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141044</t>
+          <t>147838</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172651</t>
+          <t>181473</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>175787</t>
+          <t>186718</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>163158</t>
+          <t>172383</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>187475</t>
+          <t>197738</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>333585</t>
+          <t>352069</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>311070</t>
+          <t>330199</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>353259</t>
+          <t>372491</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>29526</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44738</t>
+          <t>45736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29327</t>
+          <t>30695</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>22401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>57439</t>
+          <t>60221</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43916</t>
+          <t>46219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79243</t>
+          <t>79055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32704</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29002</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21195</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39575</t>
+          <t>41894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>48391</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36576</t>
+          <t>39523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>67026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>210244</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210244</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210244</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>446377</t>
+          <t>472257</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>446377</t>
+          <t>472257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446377</t>
+          <t>472257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>87216</t>
+          <t>85669</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80619</t>
+          <t>79239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90794</t>
+          <t>89388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>125373</t>
+          <t>125987</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117633</t>
+          <t>118305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131189</t>
+          <t>131616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,17 +1933,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>212589</t>
+          <t>211656</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203004</t>
+          <t>202082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219975</t>
+          <t>218575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17791</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>25434</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14234</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17467</t>
+          <t>17325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>114461</t>
+          <t>147098</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99847</t>
+          <t>132009</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123937</t>
+          <t>157599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>170401</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>202792</t>
+          <t>159789</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>234279</t>
+          <t>178272</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>332155</t>
+          <t>317499</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>312081</t>
+          <t>301407</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>356349</t>
+          <t>330409</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35407</t>
+          <t>36785</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11336</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40813</t>
+          <t>39652</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>48012</t>
+          <t>50457</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27623</t>
+          <t>38531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66994</t>
+          <t>66222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>65545</t>
+          <t>78896</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60710</t>
+          <t>72995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68621</t>
+          <t>82043</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>67232</t>
+          <t>74698</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61177</t>
+          <t>67087</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69762</t>
+          <t>77511</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>132776</t>
+          <t>153594</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>125570</t>
+          <t>146159</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136929</t>
+          <t>158078</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>734</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>872</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>421</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>114308</t>
+          <t>115837</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107556</t>
+          <t>109239</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>118959</t>
+          <t>120983</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>92130</t>
+          <t>94169</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84846</t>
+          <t>86671</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>98231</t>
+          <t>99739</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>206438</t>
+          <t>210007</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>196801</t>
+          <t>200633</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>213818</t>
+          <t>217667</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17881</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>26420</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>29167</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38752</t>
+          <t>38011</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>371</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>878</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>277674</t>
+          <t>313606</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>262544</t>
+          <t>296301</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>288811</t>
+          <t>325401</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>269648</t>
+          <t>315514</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>257450</t>
+          <t>303148</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>278571</t>
+          <t>325851</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>547322</t>
+          <t>629121</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>528522</t>
+          <t>607065</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>561247</t>
+          <t>645569</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>36005</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>24448</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>45812</t>
+          <t>52242</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>25620</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>18866</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>36996</t>
+          <t>39665</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>56693</t>
+          <t>64859</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43934</t>
+          <t>50146</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>75090</t>
+          <t>85904</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>17610</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -4513,67 +4513,67 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>5890</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>12991</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>5612</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>351804</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>707983</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>707983</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>707983</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>293516</t>
+          <t>342055</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>101127</t>
+          <t>330930</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>528810</t>
+          <t>349697</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>334534</t>
+          <t>390300</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>327044</t>
+          <t>382175</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>339048</t>
+          <t>395932</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>628049</t>
+          <t>732356</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>275200</t>
+          <t>720223</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>865303</t>
+          <t>741939</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>257733</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20669</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>452006</t>
+          <t>26159</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>11550</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>271597</t>
+          <t>32466</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>628377</t>
+          <t>44576</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1248024</t>
+          <t>1387320</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>748311</t>
+          <t>1354637</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1473332</t>
+          <t>1414435</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1386513</t>
+          <t>1471945</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1362623</t>
+          <t>1446899</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1420515</t>
+          <t>1496572</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2634537</t>
+          <t>2859264</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2021445</t>
+          <t>2821703</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2867653</t>
+          <t>2897449</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>376130</t>
+          <t>139328</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>146098</t>
+          <t>115632</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>899489</t>
+          <t>171463</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>148365</t>
+          <t>161669</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>122343</t>
+          <t>143916</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>168345</t>
+          <t>185979</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>524495</t>
+          <t>300998</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>289109</t>
+          <t>267562</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1167496</t>
+          <t>335956</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>20806</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>48386</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>50773</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>67086</t>
+          <t>71543</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>55048</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>88497</t>
+          <t>89490</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
